--- a/SPKnProposalAnalysis/BI Sibolga/Internal_-_BI_Sibolga_Costing_format_TJ_v4.xlsx
+++ b/SPKnProposalAnalysis/BI Sibolga/Internal_-_BI_Sibolga_Costing_format_TJ_v4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galihmujiagung/Documents/GitHub/core-itera/financial-estimations/SPKnProposalAnalysis/BI Sibolga/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB00E3E-CA1F-024D-B976-531D4815A7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E82A5C9-AB53-3847-89C7-688965215064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="34200" windowHeight="22240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ringkasan" sheetId="1" r:id="rId1"/>
@@ -8099,6 +8099,7 @@
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
